--- a/HCVData/subtyping-comparison/11-report-subtype-agreement/NS5B_CometFullSeqSubtype_4R_Subtyping_Distances.xlsx
+++ b/HCVData/subtyping-comparison/11-report-subtype-agreement/NS5B_CometFullSeqSubtype_4R_Subtyping_Distances.xlsx
@@ -431,65 +431,70 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Genotype1Distance</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Genotype2Distance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Genotype3Distance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Genotype4Distance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Genotype5Distance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Genotype6Distance</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Genotype7Distance</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Genotype8Distance</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>FirstChoiceGenotype</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>SecondChoiceGenotype</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -503,60 +508,65 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>29.603</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>29.004</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>30.712</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>16.783</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>28.169</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>30.370</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>28.085</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>16.783</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>29.603</t>
         </is>
@@ -570,60 +580,65 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>26.872</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>28.667</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>17.785</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>20.000</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>29.297</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>28.682</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>29.502</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>17.785</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>28.667</t>
         </is>
@@ -637,65 +652,70 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>434</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>26.545</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>29.885</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>29.224</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>21.659</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>30.822</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>32.420</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>33.864</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>29.107</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>21.659</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>26.545</t>
         </is>
@@ -709,55 +729,60 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>295</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>27.313</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>28.881</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>17.288</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>29.167</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>26.996</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>28.111</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>17.288</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>26.996</t>
         </is>
@@ -771,60 +796,65 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>28.228</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>29.530</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>29.882</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>15.430</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>31.173</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>29.909</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>29.964</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>15.430</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>28.228</t>
         </is>
@@ -838,60 +868,65 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>300</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>28.947</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>28.016</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>31.457</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>17.276</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>27.778</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>30.534</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>29.545</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>17.276</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>28.947</t>
         </is>
@@ -918,150 +953,155 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype1aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype1aDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Subtype1bDistance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Subtype1bDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Subtype1cDistance</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Subtype1cDistance</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Subtype1dDistance</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Subtype1eDistance</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Subtype1eDistance</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Subtype1gDistance</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Subtype1gDistance</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Subtype1hDistance</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Subtype1hDistance</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Subtype1iDistance</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Subtype1jDistance</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Subtype1kDistance</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Subtype1lDistance</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Subtype1lDistance</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Subtype1mDistance</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Subtype1mDistance</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Subtype1nDistance</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Subtype1nDistance</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Subtype1oDistance</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Subtype1oDistance</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -1088,145 +1128,150 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype2aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype2aDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Subtype2bDistance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Subtype2bDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Subtype2cDistance</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Subtype2dDistance</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Subtype2eDistance</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Subtype2fDistance</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Subtype2fDistance</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Subtype2iDistance</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Subtype2jDistance</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Subtype2jDistance</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Subtype2kDistance</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Subtype2lDistance</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Subtype2lDistance</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Subtype2mDistance</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Subtype2mDistance</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Subtype2qDistance</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Subtype2qDistance</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Subtype2rDistance</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Subtype2tDistance</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Subtype2uDistance</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Subtype2vDistance</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -1253,85 +1298,90 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype3aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype3bDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Subtype3dDistance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Subtype3eDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Subtype3gDistance</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Subtype3gDistance</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Subtype3hDistance</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Subtype3iDistance</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Subtype3iDistance</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Subtype3kDistance</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Subtype3kDistance</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -1358,145 +1408,150 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype4aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype4bDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Subtype4cDistance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Subtype4dDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Subtype4dDistance</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Subtype4fDistance</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Subtype4fDistance</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Subtype4gDistance</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Subtype4kDistance</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Subtype4kDistance</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Subtype4lDistance</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Subtype4mDistance</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Subtype4nDistance</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Subtype4oDistance</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Subtype4pDistance</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Subtype4qDistance</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Subtype4rDistance</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Subtype4sDistance</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Subtype4tDistance</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Subtype4vDistance</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Subtype4vDistance</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Subtype4wDistance</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Subtype4wDistance</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -1510,145 +1565,150 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>16.783</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>20.357</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>19.930</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>16.084</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>16.084</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>17.254</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>17.254</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>19.636</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>14.545</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>14.545</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>15.035</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>14.440</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>17.606</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>17.391</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12.587</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>17.133</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>17.754</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>17.391</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>17.690</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>14.801</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>14.801</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>19.231</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>19.231</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>4p</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>12.587</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>4l</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>15.035</t>
         </is>
@@ -1662,145 +1722,150 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>17.785</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>21.477</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>19.463</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>17.785</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>17.785</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>20.134</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>20.134</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>23.490</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>16.107</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>16.107</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>13.758</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>15.101</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>16.107</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>19.799</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>16.443</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>16.443</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>17.114</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>19.048</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>18.121</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>16.107</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>16.107</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>19.463</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>19.463</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>4l</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>13.758</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>4m</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>15.101</t>
         </is>
@@ -1814,145 +1879,150 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>434</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>21.659</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>24.828</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>19.124</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>18.391</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>18.391</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>21.101</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>21.101</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>22.120</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>20.460</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>20.460</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>18.894</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>19.816</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>20.737</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>23.041</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>19.816</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>18.664</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>17.011</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>22.989</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>20.366</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>16.129</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>16.129</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>24.312</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>24.312</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>4v</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>16.129</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>4r</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>17.011</t>
         </is>
@@ -1966,145 +2036,150 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>295</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>17.288</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>21.502</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>18.644</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>16.949</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>16.949</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>18.493</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>18.493</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>22.182</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>15.932</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>15.932</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>13.898</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>12.881</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>16.382</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>19.661</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>15.254</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>16.610</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>16.610</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>18.983</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>16.187</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>15.254</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15.254</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>18.089</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>18.089</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>4m</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>12.881</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>4l</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>13.898</t>
         </is>
@@ -2118,145 +2193,150 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>15.430</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>20.120</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>15.134</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>15.134</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>15.134</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>16.914</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>16.914</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>20.178</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>15.727</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>15.727</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>16.617</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>16.914</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>20.178</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>21.365</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>15.821</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>18.373</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>7.122</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>21.365</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>20.772</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>18.619</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>18.619</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>21.726</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>21.726</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>4r</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>7.122</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>4d</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>15.134</t>
         </is>
@@ -2270,145 +2350,150 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>300</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>17.276</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>22.667</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>17.667</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>17.667</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>17.667</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>19.333</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>19.333</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>22.333</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>20.333</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>20.333</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>16.667</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>17.333</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>19.000</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>19.333</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>15.667</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>17.667</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>16.000</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>17.172</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>20.667</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>17.333</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>17.333</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>20.000</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>20.000</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>4p</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>15.667</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>4r</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>16.000</t>
         </is>
@@ -2435,40 +2520,45 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype5aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype5bDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -2495,255 +2585,260 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype6aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype6aDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Subtype6bDistance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Subtype6cDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Subtype6dDistance</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Subtype6eDistance</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Subtype6fDistance</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Subtype6gDistance</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Subtype6hDistance</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Subtype6iDistance</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Subtype6jDistance</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Subtype6kDistance</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Subtype6lDistance</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Subtype6mDistance</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Subtype6nDistance</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Subtype6nDistance</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Subtype6oDistance</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Subtype6pDistance</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Subtype6qDistance</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Subtype6rDistance</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Subtype6sDistance</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Subtype6tDistance</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Subtype6tDistance</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Subtype6uDistance</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Subtype6vDistance</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Subtype6vDistance</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Subtype6wDistance</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Subtype6wDistance</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Subtype6xaDistance</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Subtype6xaDistance</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Subtype6xbDistance</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Subtype6xbDistance</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Subtype6xcDistance</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Subtype6xdDistance</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Subtype6xdDistance</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Subtype6xeDistance</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Subtype6xeDistance</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Subtype6xfDistance</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Subtype6xfDistance</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Subtype6xgDistance</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Subtype6xgDistance</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Subtype6xhDistance</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Subtype6xiDistance</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Subtype6xiDistance</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Subtype6xjDistance</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -2770,40 +2865,45 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype7aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype7bDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -2830,35 +2930,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype8aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>

--- a/HCVData/subtyping-comparison/11-report-subtype-agreement/NS5B_CometFullSeqSubtype_4R_Subtyping_Distances.xlsx
+++ b/HCVData/subtyping-comparison/11-report-subtype-agreement/NS5B_CometFullSeqSubtype_4R_Subtyping_Distances.xlsx
@@ -8,14 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Genotype" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_3" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_4" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_5" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_7" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_8" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_4" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -791,7 +784,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KC506776</t>
+          <t>KP347417</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -801,42 +794,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>28.228</t>
+          <t>28.947</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>29.530</t>
+          <t>28.016</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29.882</t>
+          <t>31.457</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>15.430</t>
+          <t>17.276</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>31.173</t>
+          <t>27.778</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>29.909</t>
+          <t>30.534</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>29.964</t>
+          <t>29.545</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -846,7 +839,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>15.430</t>
+          <t>17.276</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -855,78 +848,6 @@
         </is>
       </c>
       <c r="O6" t="inlineStr">
-        <is>
-          <t>28.228</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>KP347417</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4R</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>28.947</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>28.016</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>31.457</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>17.276</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>27.778</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>30.534</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>29.545</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>17.276</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
         <is>
           <t>28.947</t>
         </is>
@@ -968,461 +889,6 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Subtype1aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Subtype1aDistance</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Subtype1bDistance</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Subtype1bDistance</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Subtype1cDistance</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Subtype1cDistance</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Subtype1dDistance</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Subtype1eDistance</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Subtype1eDistance</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Subtype1gDistance</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Subtype1gDistance</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Subtype1hDistance</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Subtype1hDistance</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Subtype1iDistance</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Subtype1jDistance</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Subtype1kDistance</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Subtype1lDistance</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Subtype1lDistance</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Subtype1mDistance</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Subtype1mDistance</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Subtype1nDistance</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Subtype1nDistance</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Subtype1oDistance</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>Subtype1oDistance</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Subtype2aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Subtype2aDistance</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Subtype2bDistance</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Subtype2bDistance</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Subtype2cDistance</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Subtype2dDistance</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Subtype2eDistance</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Subtype2fDistance</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Subtype2fDistance</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Subtype2iDistance</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Subtype2jDistance</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Subtype2jDistance</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Subtype2kDistance</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Subtype2lDistance</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Subtype2lDistance</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Subtype2mDistance</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Subtype2mDistance</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Subtype2qDistance</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Subtype2qDistance</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Subtype2rDistance</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Subtype2tDistance</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Subtype2uDistance</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Subtype2vDistance</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Subtype3aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Subtype3bDistance</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Subtype3dDistance</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Subtype3eDistance</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Subtype3gDistance</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Subtype3gDistance</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Subtype3hDistance</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Subtype3iDistance</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Subtype3iDistance</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Subtype3kDistance</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Subtype3kDistance</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>Subtype4aDistance</t>
         </is>
       </c>
@@ -2188,7 +1654,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KC506776</t>
+          <t>KP347417</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2198,7 +1664,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2208,764 +1674,137 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15.430</t>
+          <t>17.276</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.120</t>
+          <t>22.667</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>15.134</t>
+          <t>17.667</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>15.134</t>
+          <t>17.667</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15.134</t>
+          <t>17.667</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>16.914</t>
+          <t>19.333</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>16.914</t>
+          <t>19.333</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>20.178</t>
+          <t>22.333</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>15.727</t>
+          <t>20.333</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>15.727</t>
+          <t>20.333</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>16.617</t>
+          <t>16.667</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>16.914</t>
+          <t>17.333</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>20.178</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>21.365</t>
+          <t>19.333</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>15.821</t>
+          <t>15.667</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>18.373</t>
+          <t>17.667</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>7.122</t>
+          <t>16.000</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>21.365</t>
+          <t>17.172</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>20.772</t>
+          <t>20.667</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>18.619</t>
+          <t>17.333</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>18.619</t>
+          <t>17.333</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>21.726</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>21.726</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>4p</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>15.667</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
           <t>4r</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>7.122</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>4d</t>
-        </is>
-      </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>15.134</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>KP347417</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4R</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>17.276</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>22.667</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>17.667</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>17.667</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>17.667</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>19.333</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>19.333</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>22.333</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>20.333</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>20.333</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>16.667</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>17.333</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>19.000</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>19.333</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>15.667</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>17.667</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
           <t>16.000</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>17.172</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>20.667</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>17.333</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>17.333</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>20.000</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>20.000</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>4p</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>15.667</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>4r</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>16.000</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Subtype5aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Subtype5bDistance</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Subtype6aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Subtype6aDistance</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Subtype6bDistance</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Subtype6cDistance</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Subtype6dDistance</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Subtype6eDistance</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Subtype6fDistance</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Subtype6gDistance</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Subtype6hDistance</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Subtype6iDistance</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Subtype6jDistance</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Subtype6kDistance</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Subtype6lDistance</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Subtype6mDistance</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Subtype6nDistance</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Subtype6nDistance</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Subtype6oDistance</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Subtype6pDistance</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Subtype6qDistance</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Subtype6rDistance</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Subtype6sDistance</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Subtype6tDistance</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Subtype6tDistance</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>Subtype6uDistance</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>Subtype6vDistance</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>Subtype6vDistance</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>Subtype6wDistance</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Subtype6wDistance</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Subtype6xaDistance</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Subtype6xaDistance</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Subtype6xbDistance</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Subtype6xbDistance</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>Subtype6xcDistance</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>Subtype6xdDistance</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>Subtype6xdDistance</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>Subtype6xeDistance</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>Subtype6xeDistance</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>Subtype6xfDistance</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>Subtype6xfDistance</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>Subtype6xgDistance</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>Subtype6xgDistance</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>Subtype6xhDistance</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>Subtype6xiDistance</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>Subtype6xiDistance</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>Subtype6xjDistance</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="BA1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Subtype7aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Subtype7bDistance</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Subtype8aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
         </is>
       </c>
     </row>
